--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
+++ b/main/ig/CodeSystem-as-cs-type-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
